--- a/Budget/transposed/budget.xlsx
+++ b/Budget/transposed/budget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\transposed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F92AD9-8422-4F77-A5C0-C76CB5725802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6A7388-E498-47DB-823A-533F938BFC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -512,7 +512,7 @@
     <col min="2" max="2" width="58.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2686,13 +2686,13 @@
         <v>7</v>
       </c>
       <c r="C95" s="3">
-        <v>6699829527</v>
+        <v>6699829526.5200005</v>
       </c>
       <c r="D95" s="3">
-        <v>31475545895</v>
+        <v>31475545894.93</v>
       </c>
       <c r="E95" s="3">
-        <v>38175375421</v>
+        <v>38175375421.459999</v>
       </c>
       <c r="F95" s="3">
         <v>10664655500</v>
@@ -2709,13 +2709,13 @@
         <v>8</v>
       </c>
       <c r="C96" s="3">
-        <v>490472582.30000001</v>
+        <v>490472582.25</v>
       </c>
       <c r="D96" s="3">
-        <v>984312234.60000002</v>
+        <v>984312234.59000003</v>
       </c>
       <c r="E96" s="3">
-        <v>1474784817</v>
+        <v>1474784816.8399999</v>
       </c>
       <c r="F96" s="3">
         <v>3019540000</v>
@@ -2732,19 +2732,19 @@
         <v>9</v>
       </c>
       <c r="C97" s="3">
-        <v>362861189.19999999</v>
+        <v>23295299702.720001</v>
       </c>
       <c r="D97" s="3">
-        <v>26812946.48</v>
+        <v>20466144369.43</v>
       </c>
       <c r="E97" s="3">
-        <v>389674135.69999999</v>
+        <v>43761444072.160004</v>
       </c>
       <c r="F97" s="3">
-        <v>6225500000</v>
+        <v>7664500000</v>
       </c>
       <c r="G97" s="3">
-        <v>6615174135.6800003</v>
+        <v>51425944072.160004</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2761,10 +2761,10 @@
         <v>72949354.549999997</v>
       </c>
       <c r="E98" s="3">
-        <v>288848672.80000001</v>
+        <v>288848672.75</v>
       </c>
       <c r="F98" s="3">
-        <v>271562000000</v>
+        <v>271562000000.10001</v>
       </c>
       <c r="G98" s="3">
         <v>271850848672.85001</v>
@@ -2778,7 +2778,7 @@
         <v>11</v>
       </c>
       <c r="C99" s="3">
-        <v>283088351.69999999</v>
+        <v>283088351.72000003</v>
       </c>
       <c r="D99" s="3">
         <v>28107274.530000001</v>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="3">
-        <v>312191149.89999998</v>
+        <v>2849428941.04</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2801,13 +2801,13 @@
         <v>12</v>
       </c>
       <c r="C100" s="3">
-        <v>613367392.20000005</v>
+        <v>613367392.23000002</v>
       </c>
       <c r="D100" s="3">
         <v>20339716.079999998</v>
       </c>
       <c r="E100" s="3">
-        <v>633707108.29999995</v>
+        <v>633707108.30999994</v>
       </c>
       <c r="F100" s="3">
         <v>3125000000</v>
@@ -2824,16 +2824,16 @@
         <v>13</v>
       </c>
       <c r="C101" s="3">
-        <v>120066559.5</v>
+        <v>120066559.48</v>
       </c>
       <c r="D101" s="3">
         <v>13384103.65</v>
       </c>
       <c r="E101" s="3">
-        <v>133450663.09999999</v>
+        <v>133450663.13</v>
       </c>
       <c r="F101" s="3">
-        <v>10411000000</v>
+        <v>10411000000.049999</v>
       </c>
       <c r="G101" s="3">
         <v>10544450663.18</v>
@@ -2850,10 +2850,10 @@
         <v>112311864</v>
       </c>
       <c r="D102" s="3">
-        <v>282383698.10000002</v>
+        <v>282383698.13</v>
       </c>
       <c r="E102" s="3">
-        <v>394695562.10000002</v>
+        <v>394695562.13</v>
       </c>
       <c r="F102" s="3">
         <v>4569000000</v>
@@ -2870,19 +2870,19 @@
         <v>15</v>
       </c>
       <c r="C103" s="3">
-        <v>697308192.60000002</v>
+        <v>697308192.55999994</v>
       </c>
       <c r="D103" s="3">
         <v>0</v>
       </c>
       <c r="E103" s="3">
-        <v>697308192.60000002</v>
+        <v>697308192.55999994</v>
       </c>
       <c r="F103" s="3">
         <v>0</v>
       </c>
       <c r="G103" s="3">
-        <v>697308192.55999994</v>
+        <v>7971967646.4799995</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -2899,7 +2899,7 @@
         <v>57531730.079999998</v>
       </c>
       <c r="E104" s="3">
-        <v>565807414.20000005</v>
+        <v>565807414.17999995</v>
       </c>
       <c r="F104" s="3">
         <v>15336833333</v>
@@ -2939,13 +2939,13 @@
         <v>18</v>
       </c>
       <c r="C106" s="3">
-        <v>1559128693</v>
+        <v>1559128693.4400001</v>
       </c>
       <c r="D106" s="3">
-        <v>3245100261</v>
+        <v>3245100260.8800001</v>
       </c>
       <c r="E106" s="3">
-        <v>4804228954</v>
+        <v>4804228954.3199997</v>
       </c>
       <c r="F106" s="3">
         <v>6058000000</v>
@@ -2985,13 +2985,13 @@
         <v>20</v>
       </c>
       <c r="C108" s="3">
-        <v>5983750263</v>
+        <v>5983750262.9399996</v>
       </c>
       <c r="D108" s="3">
-        <v>342004375.89999998</v>
+        <v>342004375.88</v>
       </c>
       <c r="E108" s="3">
-        <v>6959461747</v>
+        <v>6959461747.1199999</v>
       </c>
       <c r="F108" s="3">
         <v>11299600000</v>
@@ -3011,10 +3011,10 @@
         <v>565015287.39999998</v>
       </c>
       <c r="D109" s="3">
-        <v>109712371.7</v>
+        <v>109712371.73999999</v>
       </c>
       <c r="E109" s="3">
-        <v>674727659.10000002</v>
+        <v>674727659.13999999</v>
       </c>
       <c r="F109" s="3">
         <v>699000000</v>
@@ -3034,10 +3034,10 @@
         <v>347591067.60000002</v>
       </c>
       <c r="D110" s="3">
-        <v>788911484.5</v>
+        <v>788911484.51999998</v>
       </c>
       <c r="E110" s="3">
-        <v>1136502552</v>
+        <v>1136502552.1199999</v>
       </c>
       <c r="F110" s="3">
         <v>5460318000</v>
@@ -3054,13 +3054,13 @@
         <v>23</v>
       </c>
       <c r="C111" s="3">
-        <v>1066410186</v>
+        <v>1066410186.2</v>
       </c>
       <c r="D111" s="3">
-        <v>295920722.10000002</v>
+        <v>295920722.08999997</v>
       </c>
       <c r="E111" s="3">
-        <v>1362330908</v>
+        <v>1362330908.29</v>
       </c>
       <c r="F111" s="3">
         <v>866000000</v>
@@ -3077,13 +3077,13 @@
         <v>24</v>
       </c>
       <c r="C112" s="3">
-        <v>221583990</v>
+        <v>221583990.03</v>
       </c>
       <c r="D112" s="3">
         <v>0</v>
       </c>
       <c r="E112" s="3">
-        <v>221583990</v>
+        <v>221583990.03</v>
       </c>
       <c r="F112" s="3">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>27</v>
       </c>
       <c r="C115" s="3">
-        <v>135779993.09999999</v>
+        <v>135779993.05000001</v>
       </c>
       <c r="D115" s="3">
         <v>15107400</v>
       </c>
       <c r="E115" s="3">
-        <v>150887393.09999999</v>
+        <v>150887393.05000001</v>
       </c>
       <c r="F115" s="3">
         <v>2701500000</v>
@@ -3192,16 +3192,16 @@
         <v>29</v>
       </c>
       <c r="C117" s="3">
-        <v>138600177.30000001</v>
+        <v>138600177.31999999</v>
       </c>
       <c r="D117" s="3">
         <v>30694000</v>
       </c>
       <c r="E117" s="3">
-        <v>169294177.30000001</v>
+        <v>169294177.31999999</v>
       </c>
       <c r="F117" s="3">
-        <v>10609500000</v>
+        <v>10609500000.02</v>
       </c>
       <c r="G117" s="3">
         <v>10778794177.34</v>
@@ -3244,10 +3244,10 @@
         <v>74436821.459999993</v>
       </c>
       <c r="E119" s="3">
-        <v>332522936.69999999</v>
+        <v>332522936.66000003</v>
       </c>
       <c r="F119" s="3">
-        <v>4015000000</v>
+        <v>4015000000.0999999</v>
       </c>
       <c r="G119" s="3">
         <v>4347522936.7600002</v>
@@ -3270,7 +3270,7 @@
         <v>619936199</v>
       </c>
       <c r="F120" s="3">
-        <v>4109700000</v>
+        <v>4109700000.0999999</v>
       </c>
       <c r="G120" s="3">
         <v>4729636199.1000004</v>
@@ -3284,13 +3284,13 @@
         <v>33</v>
       </c>
       <c r="C121" s="3">
-        <v>628826114.29999995</v>
+        <v>628826114.26999998</v>
       </c>
       <c r="D121" s="3">
         <v>71619608.079999998</v>
       </c>
       <c r="E121" s="3">
-        <v>700445722.39999998</v>
+        <v>700445722.35000002</v>
       </c>
       <c r="F121" s="3">
         <v>2876000000</v>
@@ -3307,13 +3307,13 @@
         <v>34</v>
       </c>
       <c r="C122" s="3">
-        <v>14028846317</v>
+        <v>14028846316.700001</v>
       </c>
       <c r="D122" s="3">
-        <v>1483600448</v>
+        <v>1483600447.99</v>
       </c>
       <c r="E122" s="3">
-        <v>15512446765</v>
+        <v>15512446764.690001</v>
       </c>
       <c r="F122" s="3">
         <v>41330450000</v>
@@ -3353,19 +3353,19 @@
         <v>36</v>
       </c>
       <c r="C124" s="3">
-        <v>538449487.79999995</v>
+        <v>538449487.82000005</v>
       </c>
       <c r="D124" s="3">
         <v>0</v>
       </c>
       <c r="E124" s="3">
-        <v>538449487.79999995</v>
+        <v>538449487.82000005</v>
       </c>
       <c r="F124" s="3">
         <v>0</v>
       </c>
       <c r="G124" s="3">
-        <v>538449487.82000005</v>
+        <v>35317207630.279999</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -3379,10 +3379,10 @@
         <v>834738168.20000005</v>
       </c>
       <c r="D125" s="3">
-        <v>238149795.80000001</v>
+        <v>238149795.78999999</v>
       </c>
       <c r="E125" s="3">
-        <v>1072887964</v>
+        <v>1072887963.99</v>
       </c>
       <c r="F125" s="3">
         <v>2209000000</v>
